--- a/testrails-reports-example/test_posts.xlsx
+++ b/testrails-reports-example/test_posts.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -29,6 +29,9 @@
     <t>Priority</t>
   </si>
   <si>
+    <t>References</t>
+  </si>
+  <si>
     <t>Run ID</t>
   </si>
   <si>
@@ -47,13 +50,7 @@
     <t>Steps</t>
   </si>
   <si>
-    <t>Steps (References)</t>
-  </si>
-  <si>
-    <t>Steps (Status)</t>
-  </si>
-  <si>
-    <t>Tested By</t>
+    <t>Steps (Expected Result)</t>
   </si>
   <si>
     <t>Tested On</t>
@@ -62,9 +59,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Version</t>
-  </si>
-  <si>
     <t>T14</t>
   </si>
   <si>
@@ -74,10 +68,13 @@
     <t>Critical</t>
   </si>
   <si>
+    <t>JW-1.1.1</t>
+  </si>
+  <si>
     <t>R4</t>
   </si>
   <si>
-    <t>Тестирование получения списка постов содержит валидные данные</t>
+    <t>Позитивное</t>
   </si>
   <si>
     <t>Passed</t>
@@ -88,9 +85,6 @@
 </t>
   </si>
   <si>
-    <t>Irina Gracheva</t>
-  </si>
-  <si>
     <t>3/25/2025 2:58 PM</t>
   </si>
   <si>
@@ -103,6 +97,9 @@
     <t>Удаление поста валидного поста возвращает успешный результат</t>
   </si>
   <si>
+    <t>JW-1.1.3</t>
+  </si>
+  <si>
     <t>Позитивное тестирование</t>
   </si>
   <si>
@@ -110,21 +107,6 @@
   </si>
   <si>
     <t>Я запускаю через postman запрос delete на удаление поста https://jsonplaceholder.typicode.com/posts/1</t>
-  </si>
-  <si>
-    <t>T74</t>
-  </si>
-  <si>
-    <t>Приложение корректно ображается для различных устройств</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>3/26/2025 2:40 PM</t>
-  </si>
-  <si>
-    <t>Compatibility</t>
   </si>
   <si>
     <t>T16</t>
@@ -143,13 +125,13 @@
     <t>T18</t>
   </si>
   <si>
-    <t>Создание постов с помощью валидных валидные данные</t>
-  </si>
-  <si>
-    <t>Позитивное</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Я создаю новый постов с помощю postman запроса (прилагается) на адрес
+    <t>Создание постов с помощью валидных данных, включая граничные значения</t>
+  </si>
+  <si>
+    <t>JW-1.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Я создаю новый пост с помощю postman запроса (прилагается) на адрес
 https://jsonplaceholder.typicode.com/posts
 </t>
   </si>
@@ -490,10 +472,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,212 +507,162 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
       <c r="N2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="P2" t="s">
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
+      <c r="M3" t="s">
+        <v>22</v>
       </c>
       <c r="N3" t="s">
         <v>23</v>
       </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
+      <c r="M4" t="s">
+        <v>22</v>
       </c>
       <c r="N4" t="s">
         <v>23</v>
       </c>
-      <c r="O4" t="s">
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="P4" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>39</v>
+      <c r="M5" t="s">
+        <v>22</v>
       </c>
       <c r="N5" t="s">
         <v>23</v>
-      </c>
-      <c r="O5" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
